--- a/신고신저가_20260816.xlsx
+++ b/신고신저가_20260816.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="000000C0"/>
     </font>
@@ -76,13 +77,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -452,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,7 +616,74 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 일요일 아침 — 전 시장 무거래, 데이터는 8/14(금) 마감분 그대로. 신규 편입 0종목으로 스캔은 갱신이 아니라 재확인, 관전 포인트는 이번 주 유통 실적과 잭슨홀로 넘어간 구간(추정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 美(8/14): S&amp;P500 7,785.76 -0.17%·나스닥 26,729.16 -0.28%·다우 53,732.41 -0.20%. 신고가 81·신저가 8 전량 승계(NEW 0). 섹터 서열 불변 — 금융 순강도 +25(12MF PER 중앙값 15.4, 표본 161/165)로 압도적 1위, 테크서비스 +17(23.2), 헬스테크 +7, 소비서비스 +6, 에너지광물 +5. ETF는 XLE +1.4%로 주간 +7.7%·YTD 40.4% 1위 유지(호르무즈 봉쇄 지속), XLU +0.6%·XLC/XLI/XLB +0.4% / XLV -0.6%·XLK -0.4%. 다음 주 촉매는 유통 — 홈디포 목요일 실적(컨센 EPS 0.74달러, +8.8% YoY)이 7월 소매판매 -0.6% 쇼크가 일회성인지 가리는 첫 실물 확인. 엔비디아는 8/26로 그 다음 주, 잭슨홀도 이달 말</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 日(8/14): 닛케이225 68,713.80 +0.59% 4거래일 연속 상승, 52주 위치 88%. 신고가 19·신저가 2 전량 승계. 순강도 금융 +4(12MF 13.5)·테크서비스 +3·운수 +3. 업종 ETF 연간 서열은 철강·비철 YTD 53.1% 1위, 은행 50.5% 2위, 전기·정밀 41.5% 3위 — 소재·금융·정밀 3축 구도가 유지. 부동산 -6.3%·자동차 -1.0%만 연간 마이너스. 급변 승계 2종(넥슨 +19.9%, 아식스 +10.8%) 모두 8/14 실적 재료로 신규 촉매 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ 홍콩(8/14): 항셍 25,116.85 -1.10%·항셍테크 4,707.62 -1.77%. 항셍테크 YTD -14.4%·52주 위치 19%로 중화권 최약 지속. 신고가 4·신저가 2 전량 승계. 전자기술만 순강도 +2(12MF 23.7, 표본 13/17), 소비내구재·산업서비스 -1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ 中(8/14): 상해종합 3,927.18 +0.01%·CSI300 4,665.88 +0.04% 보합. 신고가 0·신저가 1(전량 승계)로 방향성 부재가 이틀째 그대로. ETF는 5G통신 +2.8%·유색금속 +1.1%·반도체 +0.8% / 의약 -1.5%·증권 -1.3%·부동산 -1.2%. 반도체 ETF YTD 47.1%로 A주 1위이나 1개월 -7.1% 조정 지속. 12MF 표본이 얇아 밸류 수치 미인용</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ①8/17~21 유통 실적(홈디포 목) — 7월 소매판매 -0.6%가 휘발유·자동차 가격 효과인지 실수요 둔화인지 판별, 미국 신고가 폭 81 유지의 전제 ②호르무즈 봉쇄 장기화 여부 — WTI 81~83달러대에서 에너지 주간 +7.7% 추가 연장 vs 인플레 재점화로 금리 되돌림, 양방향 ③금융 순강도 +25가 다음 세션에도 남는지 — 로테이션이 지속인지 한 주짜리였는지의 분기점</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ 참고: 일요일 실행이라 전 시장 무거래 — 미국·일본·홍콩·중국A 모두 8/14(금) 마감분으로, 8/15 스캔과 동일 데이터셋(NEW 0, 전 종목 승계). 텔레그램 채널 적재분은 최신이 6/29라 미사용, 회사PC 자격증명 부재로 vault pull 미수행. ETF 44/44·지수 8/8 정상 수집</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -708,19 +781,19 @@
       <c r="C2" t="n">
         <v>7785.76</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>-0.17</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="5" t="n">
         <v>0.36</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="5" t="n">
         <v>3.34</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="5" t="n">
         <v>3.79</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="5" t="n">
         <v>13.74</v>
       </c>
       <c r="I2" t="n">
@@ -746,19 +819,19 @@
       <c r="C3" t="n">
         <v>26729.16</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>-0.28</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="5" t="n">
         <v>0.14</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="5" t="n">
         <v>3.27</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="5" t="n">
         <v>0.35</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="5" t="n">
         <v>15</v>
       </c>
       <c r="I3" t="n">
@@ -784,19 +857,19 @@
       <c r="C4" t="n">
         <v>6977.94</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="5" t="n">
         <v>2.42</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>11.49</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="4" t="n">
         <v>-4.21</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="4" t="n">
         <v>-12.57</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="5" t="n">
         <v>65.58</v>
       </c>
       <c r="I4" t="n">
@@ -822,19 +895,19 @@
       <c r="C5" t="n">
         <v>68713.8</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="5" t="n">
         <v>0.59</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="5" t="n">
         <v>4.61</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="5" t="n">
         <v>1.43</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="5" t="n">
         <v>11.89</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="5" t="n">
         <v>36.5</v>
       </c>
       <c r="I5" t="n">
@@ -860,19 +933,19 @@
       <c r="C6" t="n">
         <v>3927.18</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="4" t="n">
         <v>-0.33</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="5" t="n">
         <v>1.15</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="4" t="n">
         <v>-4.95</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="4" t="n">
         <v>-1.05</v>
       </c>
       <c r="I6" t="n">
@@ -898,19 +971,19 @@
       <c r="C7" t="n">
         <v>4665.88</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="4" t="n">
         <v>-0.61</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="4" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="4" t="n">
         <v>-3.47</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="5" t="n">
         <v>0.78</v>
       </c>
       <c r="I7" t="n">
@@ -936,19 +1009,19 @@
       <c r="C8" t="n">
         <v>25116.85</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="4" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="4" t="n">
         <v>-2.15</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="5" t="n">
         <v>0.43</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="4" t="n">
         <v>-4.82</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="4" t="n">
         <v>-2</v>
       </c>
       <c r="I8" t="n">
@@ -974,19 +1047,19 @@
       <c r="C9" t="n">
         <v>4707.62</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="4" t="n">
         <v>-1.77</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="4" t="n">
         <v>-3.1</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="4" t="n">
         <v>-2.62</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="4" t="n">
         <v>-7.26</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="4" t="n">
         <v>-14.65</v>
       </c>
       <c r="I9" t="n">
@@ -1105,7 +1178,7 @@
       <c r="F2" t="n">
         <v>25</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1146,7 +1219,7 @@
       <c r="F3" t="n">
         <v>17</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1187,7 +1260,7 @@
       <c r="F4" t="n">
         <v>7</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1228,7 +1301,7 @@
       <c r="F5" t="n">
         <v>6</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1269,7 +1342,7 @@
       <c r="F6" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1310,7 +1383,7 @@
       <c r="F7" t="n">
         <v>4</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1351,7 +1424,7 @@
       <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1392,7 +1465,7 @@
       <c r="F9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1433,7 +1506,7 @@
       <c r="F10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1474,7 +1547,7 @@
       <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1515,7 +1588,7 @@
       <c r="F12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1556,7 +1629,7 @@
       <c r="F13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1597,7 +1670,7 @@
       <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1638,7 +1711,7 @@
       <c r="F15" t="n">
         <v>-1</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1923,7 +1996,7 @@
       <c r="F22" t="n">
         <v>4</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1964,7 +2037,7 @@
       <c r="F23" t="n">
         <v>3</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2003,7 +2076,7 @@
       <c r="F24" t="n">
         <v>3</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2042,7 +2115,7 @@
       <c r="F25" t="n">
         <v>2</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2083,7 +2156,7 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2122,7 +2195,7 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2161,7 +2234,7 @@
       <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2202,7 +2275,7 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2241,7 +2314,7 @@
       <c r="F30" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2674,7 +2747,7 @@
       <c r="F41" t="n">
         <v>2</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2715,7 +2788,7 @@
       <c r="F42" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2756,7 +2829,7 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2795,7 +2868,7 @@
       <c r="F44" t="n">
         <v>-1</v>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2836,7 +2909,7 @@
       <c r="F45" t="n">
         <v>-1</v>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3392,7 +3465,7 @@
       <c r="F59" t="n">
         <v>-1</v>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -4096,30 +4169,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4140,90 +4214,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -4245,58 +4324,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>8/14 -0.4%·주간 +1.1%·YTD 32.3% 2위. 순강도 +17로 강세 판정이나 고가권 종목 당일 조정 병행</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <v>32.3</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4316,58 +4400,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>8/14 -0.6%로 당일 최약, 3개월 +14.6%는 미국 최상위. 순강도 +7로 저변은 유지</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="9" t="n">
         <v>14.6</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>7</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4387,58 +4476,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>8/14 -0.2%지만 순강도 +25로 미국 1위, 12MF PER 15.4. 지역은행·캐나다은행 전방위 신고가</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="9" t="n">
         <v>13.8</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="9" t="n">
         <v>7.1</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4458,58 +4552,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>8/14 -0.2%·주간 -1.4%·YTD -0.6%로 11개 중 10위. 7월 소매판매 -0.6% 부담 반영(추정)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4529,58 +4628,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>8/14 +0.4%로 반등했으나 YTD -3.5% 최하위. 3개월 -3.3%로 추세 회복 미확인</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-3.5</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4600,58 +4704,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>8/14 +0.4%·YTD 20.9% 3위. 3개월 +7.1%로 완만한 우상향 유지</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="9" t="n">
         <v>7.1</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="9" t="n">
         <v>20.9</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4671,58 +4780,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>8/14 +0.1%·YTD 12.2%. 방어 성격대로 변동 폭 작고 순위 중위권 고착</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4742,58 +4856,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>8/14 +1.4%·주간 +7.7%·YTD 40.4%로 전 섹터 1위. 호르무즈 봉쇄 지속·WTI 81~83달러대가 동력</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="9" t="n">
         <v>7.7</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H9" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="9" t="n">
         <v>40.4</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4813,58 +4932,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>8/14 +0.6%로 당일 상위, 다만 1개월 -2.6%. 금리 되돌림 헤지 성격 매수 추정</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="9" t="n">
         <v>5.2</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4884,58 +5008,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>8/14 +0.4%·YTD 16.8% 4위이나 주간 -0.6%로 단기 숨 고르기</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4955,58 +5084,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>8/14 +0.3%·YTD 13.9% 5위. 1개월 -0.4%로 금리 눈치 보기 지속</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5026,58 +5160,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="H13" s="9" t="n">
         <v>11.7</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>7</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5097,58 +5232,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>4.2</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="9" t="n">
         <v>9.4</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>9</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5168,58 +5304,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="9" t="n">
         <v>-2.3</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="H15" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>9.1</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>11</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5239,58 +5376,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="H16" s="9" t="n">
         <v>3.6</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5310,58 +5448,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="9" t="n">
         <v>5.9</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="H17" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>14</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5381,58 +5520,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="H18" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5452,58 +5592,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>6.7</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="9" t="n">
         <v>53.1</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5523,58 +5664,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>6</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5594,58 +5736,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="9" t="n">
         <v>5.4</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="9" t="n">
         <v>15.2</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5665,58 +5808,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="9" t="n">
         <v>7.6</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="9" t="n">
         <v>8.1</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="9" t="n">
         <v>16.2</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>10</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5736,58 +5880,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>15</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5807,58 +5952,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="9" t="n">
         <v>6.7</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="9" t="n">
         <v>5.2</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>13</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5878,58 +6024,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="6" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="9" t="n">
         <v>9.4</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="9" t="n">
         <v>-8.5</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="9" t="n">
         <v>18.8</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>8</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5949,58 +6096,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="H26" s="9" t="n">
         <v>9.6</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>12</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6020,58 +6168,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="9" t="n">
         <v>23.5</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="9" t="n">
         <v>50.5</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6091,58 +6240,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="9" t="n">
         <v>9.6</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="9" t="n">
         <v>28.4</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6162,58 +6312,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="9" t="n">
         <v>-4.6</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="9" t="n">
         <v>-6.6</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="9" t="n">
         <v>-6.3</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6233,58 +6384,59 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="F30" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="O30" s="9" t="n">
         <v>-13.7</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="9" t="n">
         <v>-15.3</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="9" t="n">
         <v>-14.2</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="U30" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6304,58 +6456,59 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="F31" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>-5.7</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>-14.1</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="S31" s="9" t="n">
         <v>-23.2</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="U31" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6375,56 +6528,57 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="9" t="n">
         <v>-3.1</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="H32" s="9" t="n">
         <v>-6.9</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="9" t="n">
         <v>-14.4</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>2</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="9" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="9" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6442,58 +6596,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>8/14 +0.8%·YTD 47.1%로 A주 1위 유지, 다만 1개월 -7.1%로 단기 조정 최심</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="9" t="n">
         <v>-7.1</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="9" t="n">
         <v>47.1</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="Q33" s="9" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="S33" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="U33" s="9" t="n">
         <v>46.6</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6513,58 +6672,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>8/14 +0.8%·YTD 33.5% 3위. 1개월 -5.1%로 반도체와 동조한 성장주 되돌림</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="9" t="n">
         <v>-5.1</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="9" t="n">
         <v>33.5</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="U34" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6584,58 +6748,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>8/14 +2.8%로 A주 당일 1위·주간 +3.0%. 1개월 -8.3% 낙폭 되돌림 성격 추정</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="H35" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="9" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="O35" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="Q35" s="9" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="S35" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="U35" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6655,56 +6824,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>8/14 +0.6%·1개월 +4.3%로 바닥 다지기, 3개월 -17.9%·YTD -10.7%로 추세는 여전히 하락</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="9" t="n">
         <v>4.3</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="9" t="n">
         <v>-17.9</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>9</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="9" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6722,58 +6896,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>8/14 +0.3%·1개월 +2.9%. 3개월 -16.2%·YTD -16.1%로 A주 하위권 고착</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="F37" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="G37" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="H37" s="9" t="n">
         <v>-16.2</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="9" t="n">
         <v>-16.1</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>11</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="O37" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="Q37" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="S37" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="U37" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6793,56 +6972,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>8/14 +0.2%·1개월 +4.7%로 반등 시도, 3개월 -21.4%로 A주 최대 낙폭 섹터</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="H38" s="9" t="n">
         <v>-21.4</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="9" t="n">
         <v>-10.1</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>7</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="O38" s="9" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6860,58 +7044,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>8/14 -1.8%로 A주 당일 최약·YTD -17.7% 12위. 소비 부진 직격 지속</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="9" t="n">
         <v>-17.7</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>12</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="S39" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="U39" s="9" t="n">
         <v>336.4</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6931,58 +7120,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>8/14 -0.7%·1개월 +1.9%. 배당 방어 수요로 하방은 제한되나 YTD -3.2%</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="G40" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="H40" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="I40" s="9" t="n">
         <v>-3.2</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>6</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="9" t="n">
         <v>42.6</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="O40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="Q40" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="S40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="U40" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7002,58 +7196,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>8/14 +1.1%·1개월 +9.6%로 A주 1개월 1위. 주간 -4.8%로 변동성은 큰 편</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="G41" s="9" t="n">
         <v>9.6</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="H41" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>5</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="O41" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="S41" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="U41" s="9" t="n">
         <v>43.2</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7073,58 +7272,63 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>8/14 -1.2%·YTD -18.3%로 A주 최하위. 3개월 -13.4%로 반등 신호 미확인</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="F42" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>13</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="S42" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="U42" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7144,58 +7348,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>8/14 -1.3%·1개월 -2.3%. 거래대금 부진 국면에서 상대 약세(추정)</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="F43" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="G43" s="9" t="n">
         <v>-2.3</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="H43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="I43" s="9" t="n">
         <v>-10.2</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>8</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="Q43" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="S43" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="U43" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7215,58 +7424,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>8/14 -1.5%지만 3개월 +13.2%로 A주 1위, YTD +4.5%로 플러스 4개 중 하나</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="F44" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="I44" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="9" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="S44" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="U44" s="9" t="n">
         <v>62.9</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7286,58 +7500,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>8/14 -1.6%·YTD -15.1%. 백주와 함께 소비 관련 동반 약세 지속</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="F45" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="H45" s="9" t="n">
         <v>-3.9</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="9" t="n">
         <v>-15.1</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="S45" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="U45" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7349,7 +7568,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-1.9"/>
@@ -7361,7 +7580,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-4.8"/>
@@ -7373,7 +7592,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-8.300000000000001"/>
@@ -7385,7 +7604,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-21.4"/>
@@ -7397,7 +7616,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-18.3"/>
@@ -7409,7 +7628,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -7421,7 +7640,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -7433,7 +7652,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -7445,7 +7664,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -7457,7 +7676,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -7469,7 +7688,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -7583,7 +7802,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7632,10 +7851,10 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7684,10 +7903,10 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7740,10 +7959,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7794,10 +8013,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7846,10 +8065,10 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7902,10 +8121,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7954,10 +8173,10 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8006,10 +8225,10 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8058,10 +8277,10 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8114,10 +8333,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8166,10 +8385,10 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8222,10 +8441,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N13" s="7" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8278,10 +8497,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="7" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8330,14 +8549,14 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>(전일) 엔브리지(캐나다 에너지 파이프라인): 개별 촉매 미확인 — 유가 강세에도 소외, 레버리지 부담 추정</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8390,10 +8609,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="7" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8446,10 +8665,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N17" s="7" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8502,10 +8721,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N18" s="7" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8554,10 +8773,10 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8606,14 +8825,14 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" s="7" t="inlineStr">
+      <c r="N20" s="10" t="inlineStr">
         <is>
           <t>(전일) 케이던스디자인시스템즈(반도체 설계 EDA 소프트웨어): 소프트웨어 전반 조정 속 장중 52주 저가 터치 후 반등, 개별 촉매 미확인</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8662,14 +8881,14 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr">
+      <c r="N21" s="10" t="inlineStr">
         <is>
           <t>(전일) 카바나(중고차 온라인 플랫폼): 개별 촉매 미확인 — 실적 개선 기대 수급 추정</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8718,10 +8937,10 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="7" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8770,10 +8989,10 @@
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8826,10 +9045,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N24" s="7" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8878,14 +9097,14 @@
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr">
-        <is>
-          <t>(전일) 누홀딩스(브라질 디지털은행): 2분기 순이익 첫 10억달러 돌파(+49%), 컨센 상회</t>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>누홀딩스(브라질 디지털은행): 8/14 세션 그대로 — 2분기 순이익 첫 10억달러 돌파(+49%)·컨센 상회, 신규 촉매 없음</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8934,10 +9153,10 @@
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8982,10 +9201,10 @@
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9034,10 +9253,10 @@
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" s="7" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9086,10 +9305,10 @@
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" s="7" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9138,10 +9357,10 @@
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" s="7" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9194,10 +9413,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N31" s="7" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9248,10 +9467,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N32" s="7" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9300,10 +9519,10 @@
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" s="7" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9352,10 +9571,10 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" s="7" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9404,10 +9623,10 @@
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9454,14 +9673,14 @@
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" s="7" t="inlineStr">
+      <c r="N36" s="10" t="inlineStr">
         <is>
           <t>(전일) 아틀라시안(협업SW Jira·Confluence): 2분기 매출 28%↑·클라우드 31% 가속, Rovo AI 견인</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9514,10 +9733,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N37" s="7" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9566,10 +9785,10 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="7" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9620,14 +9839,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N39" s="7" t="inlineStr">
+      <c r="N39" s="10" t="inlineStr">
         <is>
           <t>(전일) 몽고DB(NoSQL 데이터베이스 SaaS): RBC·오펜하이머 목표가 대폭 상향, Atlas 성장 기대</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9680,10 +9899,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N40" s="7" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9732,10 +9951,10 @@
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" s="7" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9784,10 +10003,10 @@
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" s="7" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9836,10 +10055,10 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" s="7" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9892,10 +10111,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N44" s="7" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9948,10 +10167,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N45" s="7" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10000,14 +10219,14 @@
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" s="7" t="inlineStr">
+      <c r="N46" s="10" t="inlineStr">
         <is>
           <t>(전일) 폭스코퍼레이션(미디어·방송): FY26 4분기 매출 28%↑, 튜비 최대 실적·월드컵 광고 효과</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10056,10 +10275,10 @@
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" s="7" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10108,10 +10327,10 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" s="7" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10160,10 +10379,10 @@
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" s="7" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10212,10 +10431,10 @@
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" s="7" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10264,14 +10483,14 @@
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" s="7" t="inlineStr">
+      <c r="N51" s="10" t="inlineStr">
         <is>
           <t>(전일) 태피스트리(코치·케이트스페이드 핸드백): 4Q 서프라이즈에도 FY27 매출 가이던스 부진에 급락</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10324,10 +10543,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N52" s="7" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10380,10 +10599,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N53" s="7" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10436,10 +10655,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N54" s="7" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10488,10 +10707,10 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" s="7" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10540,14 +10759,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N56" s="7" t="inlineStr">
+      <c r="N56" s="10" t="inlineStr">
         <is>
           <t>(전일) 루브릭(데이터 백업·랜섬웨어 복구 SW): 보안·SW 랠리, BTIG 목표가 109달러 상향 여진</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10596,14 +10815,14 @@
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" s="7" t="inlineStr">
+      <c r="N57" s="10" t="inlineStr">
         <is>
           <t>(전일) TPG(대체투자 운용사): 개별 뉴스 없음, 워크데이 인수설발 PE 딜 훈풍 추정</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10650,10 +10869,10 @@
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" s="7" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10706,10 +10925,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N59" s="7" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10758,10 +10977,10 @@
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" s="7" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10814,10 +11033,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N61" s="7" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10864,10 +11083,10 @@
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" s="7" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10916,10 +11135,10 @@
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" s="7" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10968,10 +11187,10 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" s="7" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11024,14 +11243,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N65" s="7" t="inlineStr">
+      <c r="N65" s="10" t="inlineStr">
         <is>
           <t>(전일) 롤린스(해충방제 서비스): 2분기 EPS 0.32달러로 컨센 하회·경영진 교체 우려로 52주 신저가</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11084,10 +11303,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N66" s="7" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11140,10 +11359,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N67" s="7" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11190,10 +11409,10 @@
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" s="7" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11246,10 +11465,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N69" s="7" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11298,10 +11517,10 @@
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" s="7" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11354,10 +11573,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N71" s="7" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11406,14 +11625,14 @@
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" s="7" t="inlineStr">
+      <c r="N72" s="10" t="inlineStr">
         <is>
           <t>(전일) 뉴로크린(신경정신질환 신약 개발): 프래더윌리 치료제 Vykat 사망사례 안전성 우려 보도</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11462,10 +11681,10 @@
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" s="7" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11516,10 +11735,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N74" s="7" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11572,14 +11791,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N75" s="7" t="inlineStr">
+      <c r="N75" s="10" t="inlineStr">
         <is>
           <t>(전일) 무그(항공우주·방산 정밀제어시스템): 3분기 실적 호조·FY26 매출 가이던스 44억달러로 상향</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11628,10 +11847,10 @@
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" s="7" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11680,10 +11899,10 @@
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" s="7" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11732,14 +11951,14 @@
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" s="7" t="inlineStr">
+      <c r="N78" s="10" t="inlineStr">
         <is>
           <t>(전일) 헤클라마이닝(미국 은 광산): 개별 촉매 미확인 — 은·소재 섹터 강세 동조 추정</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11788,14 +12007,14 @@
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" s="7" t="inlineStr">
+      <c r="N79" s="10" t="inlineStr">
         <is>
           <t>(전일) 크라토스디펜스(무인기·방산 시스템): 재블린 시커·대드론 1.56억달러 등 수주 모멘텀</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11844,14 +12063,14 @@
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" s="7" t="inlineStr">
+      <c r="N80" s="10" t="inlineStr">
         <is>
           <t>(전일) 도큐사인(전자서명·계약관리 SaaS): 개별 뉴스 없이 소프트웨어 업종 전반 랠리에 동반 급등</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11900,10 +12119,10 @@
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" s="7" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11956,10 +12175,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N82" s="7" t="inlineStr"/>
+      <c r="N82" s="10" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12010,10 +12229,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N83" s="7" t="inlineStr"/>
+      <c r="N83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12066,10 +12285,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N84" s="7" t="inlineStr"/>
+      <c r="N84" s="10" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12120,14 +12339,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N85" s="7" t="inlineStr">
+      <c r="N85" s="10" t="inlineStr">
         <is>
           <t>(전일) 글라우코스(녹내장·각막질환 의료기기): 2분기 매출 급증·2026년 가이던스 상향, 목표주가 잇단 상향</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="inlineStr">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12180,10 +12399,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N86" s="7" t="inlineStr"/>
+      <c r="N86" s="10" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12236,14 +12455,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N87" s="7" t="inlineStr">
+      <c r="N87" s="10" t="inlineStr">
         <is>
           <t>(전일) 달링인그리디언츠(동물부산물·재생연료 원료): 2분기 사상최대 실적·자사주 10억달러 여진</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12296,10 +12515,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N88" s="7" t="inlineStr"/>
+      <c r="N88" s="10" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="A89" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12344,14 +12563,14 @@
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" s="7" t="inlineStr">
+      <c r="N89" s="10" t="inlineStr">
         <is>
           <t>(전일) 허트8(비트코인 채굴·데이터센터): 2분기 순손실 전환, 75억달러 확장 파이낸싱 부담</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12404,7 +12623,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N90" s="7" t="inlineStr"/>
+      <c r="N90" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N90"/>
@@ -12510,7 +12729,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12557,10 +12776,10 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12613,14 +12832,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 어드반테스트(반도체 테스터 장비): AI 반도체 테스터 수요 급증·실적 상향으로 급등</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12673,14 +12892,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 미즈호FG(3대 메가뱅크): 당일 -1.5% 하락에도 장중 고가가 52주 신고가 터치, 은행 랠리 연장</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12727,14 +12946,14 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) 미쓰비시중공업(중공업·방위산업): 방위비 증액 기대와 1분기 실적 호조 지속으로 상승</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12781,14 +13000,14 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>(전일) NTT(통신 1위): 개별 뉴스 없음, 금리·방어주 수급에 신고가 진입 추정</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12839,14 +13058,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 파나소닉(가전·전장·전지): 개별 뉴스 없음, 엔약세·전기정밀 섹터 강세 동조 추정</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12895,14 +13114,14 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) 닌텐도(게임기·소프트웨어): 인도네시아 스위치·스위치2 발매 추진 보도(지지통신)로 4개월래 최고가</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12951,14 +13170,14 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>(전일) NEC(IT서비스·통신장비): 당일 촉매 미확인, 1Q 순이익 +157%·가이던스 상향 모멘텀 연장 추정</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13005,14 +13224,14 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr">
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>(전일) 다이킨(공조·에어컨): 8/4 1Q 순이익 -1.7% 발표 후 약세 지속, 당일 신규 악재는 없음</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13065,14 +13284,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) 리소나홀딩스(대형 은행지주): 정부의 조기 금리인상 지지 보도로 은행주 일제 급등</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13125,14 +13344,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="7" t="inlineStr">
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>(전일) 스미토모미쓰이트러스트그룹(신탁은행 지주): 정부의 조기 금리인상 지지 보도로 은행주 일제 급등</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13179,14 +13398,14 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr">
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>(전일) 미쓰비시지쇼(오피스 부동산 디벨로퍼): 특별한 뉴스 없음, 부동산 섹터 약세 수급 추정</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13233,14 +13452,14 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="7" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>(전일) 테루모(의료기기·수액세트): FY27.3 영업이익 2245억→2575억엔 상향, 1Q 순이익 68%↑</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13291,14 +13510,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N15" s="7" t="inlineStr">
-        <is>
-          <t>(전일) 아식스(스포츠용품 제조): 경상익 15% 상향 1890억엔, 사상 첫 매출 1조엔 전망</t>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>아식스(스포츠용품 제조): 8/14 세션 그대로 — 경상익 15% 상향 1890억엔·사상 첫 매출 1조엔 전망, 신규 촉매 없음</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13349,14 +13568,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="7" t="inlineStr">
+      <c r="N16" s="10" t="inlineStr">
         <is>
           <t>(전일) LY Corporation(포털·메신저·페이페이 핀테크): 신규 촉매 없음, 8월초 페이페이발 호실적 모멘텀 연장</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13409,14 +13628,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N17" s="7" t="inlineStr">
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>(전일) 니혼유센(벌크·컨테이너 해운): 해운 3종 동반 강세, 컨테이너 운임 기대(당일 개별뉴스 미확인)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13463,14 +13682,14 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="7" t="inlineStr">
-        <is>
-          <t>(전일) 넥슨(온라인게임 퍼블리셔): 2분기 영업익 313억엔으로 컨센 240억엔 상회, 특별배당 415엔</t>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>넥슨(온라인게임 퍼블리셔): 8/14 세션 그대로 — 2분기 영업익 313억엔으로 컨센 240억엔 상회·특별배당 415엔, 신규 촉매 없음</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13519,10 +13738,10 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13575,14 +13794,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="7" t="inlineStr">
+      <c r="N20" s="10" t="inlineStr">
         <is>
           <t>(전일) 지바은행(지방은행): 정부의 조기 금리인상 지지 보도로 은행주 일제 급등</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13635,10 +13854,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N21" s="7" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13691,7 +13910,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N22" s="7" t="inlineStr">
+      <c r="N22" s="10" t="inlineStr">
         <is>
           <t>(전일) 가와사키기선(컨테이너선 해운): 해운 3종 동반 강세, 컨테이너 운임 기대(당일 개별뉴스 미확인)</t>
         </is>
@@ -13801,7 +14020,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13854,14 +14073,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) 레노버(PC·서버 세계 1위): FY26/27 1분기 매출 43%·조정순이익 176% 급증, AI서버 매출 사상 최고</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13910,14 +14129,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 차오저우싼환(적층세라믹콘덴서 MLCC·세라믹부품): AI 인프라용 고급 MLCC 공급부족·가격인상 수혜</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13968,14 +14187,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) CLP홀딩스(홍콩 최대 전력회사, 발전·송배전): 특별한 뉴스 없음(유틸리티 방어주 수급 흐름 추정)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14028,14 +14247,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) SITC인터내셔널(아시아 역내 컨테이너 해운): 개별 뉴스 없음, 중간실적 앞둔 해운 강세 동조 추정</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14086,14 +14305,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>(전일) 중국철도건설(대형 인프라·철도 시공): 특별한 뉴스 없음(국유 건설섹터 수급 부진 추정)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14138,7 +14357,7 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 니오(중국 프리미엄 전기차): 특별한 뉴스 없음(전기차 섹터 수급 약세 추정)</t>
         </is>
@@ -14248,7 +14467,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14297,7 +14516,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) 선전 자리촹(PCB·전자제조서비스, 8/4 상장): 개별 악재 없음, 상장 초기 급등 후 조정 지속 추정</t>
         </is>
